--- a/prediction results.xlsx
+++ b/prediction results.xlsx
@@ -1,31 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\EnergeticGraph\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor Projects\EnergeticGraph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CE8409-34B7-4601-A6A1-0032C4ABDE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07049A9-07FD-45BF-93C6-6ABD6146BDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="31785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="6100" windowWidth="28800" windowHeight="15370" activeTab="4" xr2:uid="{89EC946F-DC53-429F-91F6-32650855A236}"/>
   </bookViews>
   <sheets>
-    <sheet name="KernelRidge" sheetId="1" r:id="rId1"/>
+    <sheet name="Kernel Ridge" sheetId="1" r:id="rId1"/>
+    <sheet name="SVR" sheetId="2" r:id="rId2"/>
+    <sheet name="Random Forest" sheetId="3" r:id="rId3"/>
+    <sheet name="XGBoost" sheetId="4" r:id="rId4"/>
+    <sheet name="XGBoost (Coulomb)" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
   <si>
     <t>property</t>
   </si>
@@ -71,16 +86,15 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -100,19 +114,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{7517A7B9-DA41-4492-AC62-95B9CBCEB1EB}"/>
+    <cellStyle name="Excel Built-in Percent" xfId="2" xr:uid="{744D70DF-7DDE-473D-8014-99E02BAEC3D9}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -138,39 +151,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -203,9 +216,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -238,6 +268,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -299,13 +346,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -314,6 +354,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -378,30 +425,50 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{162FD3F5-A2F3-4737-B403-30054D213DAE}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,124 +488,756 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>0.88800000000000001</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>0.77569999999999995</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>6.5799999999999997E-2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2">
         <v>5.4399999999999997E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>0.98129999999999995</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>0.95230000000000004</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>292.40589999999997</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <v>231.30420000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>0.75539999999999996</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>0.56979999999999997</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>76.335499999999996</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>0.1113</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <v>50.082799999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>0.97789999999999999</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>0.94199999999999995</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>2.0305</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>0.1008</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <v>1.5709</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>0.92320000000000002</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>0.86019999999999996</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>627.75739999999996</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>0.14710000000000001</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <v>457.5496</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>0.94430000000000003</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>0.79400000000000004</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>173.37459999999999</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>0.76739999999999997</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7">
         <v>114.2212</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719D0C69-70FA-48C5-B803-41A9A261E93C}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0.87639999999999996</v>
+      </c>
+      <c r="C2">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="D2">
+        <v>5.9200000000000003E-2</v>
+      </c>
+      <c r="E2">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="F2">
+        <v>4.7699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>0.93920000000000003</v>
+      </c>
+      <c r="C3">
+        <v>0.91549999999999998</v>
+      </c>
+      <c r="D3">
+        <v>388.87860000000001</v>
+      </c>
+      <c r="E3">
+        <v>5.7799999999999997E-2</v>
+      </c>
+      <c r="F3">
+        <v>291.76839999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>0.72340000000000004</v>
+      </c>
+      <c r="C4">
+        <v>0.28820000000000001</v>
+      </c>
+      <c r="D4">
+        <v>98.194900000000004</v>
+      </c>
+      <c r="E4">
+        <v>0.14319999999999999</v>
+      </c>
+      <c r="F4">
+        <v>54.759500000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="C5">
+        <v>0.93420000000000003</v>
+      </c>
+      <c r="D5">
+        <v>2.1627000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.10730000000000001</v>
+      </c>
+      <c r="F5">
+        <v>1.6527000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>0.73180000000000001</v>
+      </c>
+      <c r="C6">
+        <v>0.66879999999999995</v>
+      </c>
+      <c r="D6">
+        <v>966.25300000000004</v>
+      </c>
+      <c r="E6">
+        <v>0.22650000000000001</v>
+      </c>
+      <c r="F6">
+        <v>691.13220000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0.67559999999999998</v>
+      </c>
+      <c r="C7">
+        <v>0.59430000000000005</v>
+      </c>
+      <c r="D7">
+        <v>243.2944</v>
+      </c>
+      <c r="E7">
+        <v>1.0768</v>
+      </c>
+      <c r="F7">
+        <v>171.20609999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9925CAE-27CB-45B8-BB86-BFB93AAA30D8}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0.94259999999999999</v>
+      </c>
+      <c r="C2">
+        <v>0.82010000000000005</v>
+      </c>
+      <c r="D2">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="E2">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="F2">
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="C3">
+        <v>0.95679999999999998</v>
+      </c>
+      <c r="D3">
+        <v>278.21260000000001</v>
+      </c>
+      <c r="E3">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="F3">
+        <v>217.05670000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>0.95930000000000004</v>
+      </c>
+      <c r="C4">
+        <v>0.67430000000000001</v>
+      </c>
+      <c r="D4">
+        <v>66.418499999999995</v>
+      </c>
+      <c r="E4">
+        <v>9.6799999999999997E-2</v>
+      </c>
+      <c r="F4">
+        <v>36.166800000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="C5">
+        <v>0.95250000000000001</v>
+      </c>
+      <c r="D5">
+        <v>1.8374999999999999</v>
+      </c>
+      <c r="E5">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="F5">
+        <v>1.4157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>0.97160000000000002</v>
+      </c>
+      <c r="C6">
+        <v>0.83950000000000002</v>
+      </c>
+      <c r="D6">
+        <v>672.69640000000004</v>
+      </c>
+      <c r="E6">
+        <v>0.15770000000000001</v>
+      </c>
+      <c r="F6">
+        <v>487.69139999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0.97289999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.76580000000000004</v>
+      </c>
+      <c r="D7">
+        <v>184.87350000000001</v>
+      </c>
+      <c r="E7">
+        <v>0.81830000000000003</v>
+      </c>
+      <c r="F7">
+        <v>116.2313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FED6D5C-92F2-433E-A07F-C9221DC9F56E}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0.92769999999999997</v>
+      </c>
+      <c r="C2">
+        <v>0.79569999999999996</v>
+      </c>
+      <c r="D2">
+        <v>6.4799999999999996E-2</v>
+      </c>
+      <c r="E2">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="F2">
+        <v>5.1799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="C3">
+        <v>0.95820000000000005</v>
+      </c>
+      <c r="D3">
+        <v>301.88080000000002</v>
+      </c>
+      <c r="E3">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="F3">
+        <v>200.01070000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>0.87080000000000002</v>
+      </c>
+      <c r="C4">
+        <v>0.66190000000000004</v>
+      </c>
+      <c r="D4">
+        <v>61.226300000000002</v>
+      </c>
+      <c r="E4">
+        <v>8.7599999999999997E-2</v>
+      </c>
+      <c r="F4">
+        <v>39.7517</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>0.99260000000000004</v>
+      </c>
+      <c r="C5">
+        <v>0.94159999999999999</v>
+      </c>
+      <c r="D5">
+        <v>2.1560000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.1045</v>
+      </c>
+      <c r="F5">
+        <v>1.3153999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>0.95420000000000005</v>
+      </c>
+      <c r="C6">
+        <v>0.85089999999999999</v>
+      </c>
+      <c r="D6">
+        <v>593.97299999999996</v>
+      </c>
+      <c r="E6">
+        <v>0.13739999999999999</v>
+      </c>
+      <c r="F6">
+        <v>478.46690000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0.96619999999999995</v>
+      </c>
+      <c r="C7">
+        <v>0.83220000000000005</v>
+      </c>
+      <c r="D7">
+        <v>144.36969999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.57740000000000002</v>
+      </c>
+      <c r="F7">
+        <v>110.27249999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689E851C-92EB-4238-AD5F-CA3B296E8810}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0.98009999999999997</v>
+      </c>
+      <c r="C2">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="D2">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E2">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="F2">
+        <v>4.7600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0.89029999999999998</v>
+      </c>
+      <c r="D3">
+        <v>489.19229999999999</v>
+      </c>
+      <c r="E3">
+        <v>7.1800000000000003E-2</v>
+      </c>
+      <c r="F3">
+        <v>336.40620000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0.77890000000000004</v>
+      </c>
+      <c r="D4">
+        <v>49.514699999999998</v>
+      </c>
+      <c r="E4">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="F4">
+        <v>31.116199999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0.87309999999999999</v>
+      </c>
+      <c r="D5">
+        <v>3.1781000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.154</v>
+      </c>
+      <c r="F5">
+        <v>2.1715</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0.81540000000000001</v>
+      </c>
+      <c r="D6">
+        <v>660.88729999999998</v>
+      </c>
+      <c r="E6">
+        <v>0.15290000000000001</v>
+      </c>
+      <c r="F6">
+        <v>465.59859999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0.76449999999999996</v>
+      </c>
+      <c r="D7">
+        <v>171.05240000000001</v>
+      </c>
+      <c r="E7">
+        <v>0.68410000000000004</v>
+      </c>
+      <c r="F7">
+        <v>115.4483</v>
       </c>
     </row>
   </sheetData>

--- a/prediction results.xlsx
+++ b/prediction results.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor Projects\EnergeticGraph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07049A9-07FD-45BF-93C6-6ABD6146BDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0827AD4A-4CB0-47B2-9FCE-63459C847C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="6100" windowWidth="28800" windowHeight="15370" activeTab="4" xr2:uid="{89EC946F-DC53-429F-91F6-32650855A236}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{89EC946F-DC53-429F-91F6-32650855A236}"/>
   </bookViews>
   <sheets>
     <sheet name="Kernel Ridge" sheetId="1" r:id="rId1"/>
     <sheet name="SVR" sheetId="2" r:id="rId2"/>
     <sheet name="Random Forest" sheetId="3" r:id="rId3"/>
     <sheet name="XGBoost" sheetId="4" r:id="rId4"/>
-    <sheet name="XGBoost (Coulomb)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
   <si>
     <t>property</t>
   </si>
@@ -1085,162 +1084,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689E851C-92EB-4238-AD5F-CA3B296E8810}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>0.98009999999999997</v>
-      </c>
-      <c r="C2">
-        <v>0.81299999999999994</v>
-      </c>
-      <c r="D2">
-        <v>6.2E-2</v>
-      </c>
-      <c r="E2">
-        <v>3.7699999999999997E-2</v>
-      </c>
-      <c r="F2">
-        <v>4.7600000000000003E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>0.89029999999999998</v>
-      </c>
-      <c r="D3">
-        <v>489.19229999999999</v>
-      </c>
-      <c r="E3">
-        <v>7.1800000000000003E-2</v>
-      </c>
-      <c r="F3">
-        <v>336.40620000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>0.77890000000000004</v>
-      </c>
-      <c r="D4">
-        <v>49.514699999999998</v>
-      </c>
-      <c r="E4">
-        <v>7.0900000000000005E-2</v>
-      </c>
-      <c r="F4">
-        <v>31.116199999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0.87309999999999999</v>
-      </c>
-      <c r="D5">
-        <v>3.1781000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.154</v>
-      </c>
-      <c r="F5">
-        <v>2.1715</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0.81540000000000001</v>
-      </c>
-      <c r="D6">
-        <v>660.88729999999998</v>
-      </c>
-      <c r="E6">
-        <v>0.15290000000000001</v>
-      </c>
-      <c r="F6">
-        <v>465.59859999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0.76449999999999996</v>
-      </c>
-      <c r="D7">
-        <v>171.05240000000001</v>
-      </c>
-      <c r="E7">
-        <v>0.68410000000000004</v>
-      </c>
-      <c r="F7">
-        <v>115.4483</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>